--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-29).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-29).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-182</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 1.755.957,71</t>
-  </si>
-  <si>
-    <t>R$ 9.145,61
-R$ 9.271,73</t>
-  </si>
-  <si>
-    <t>(5.5%)
-(4.2%)</t>
-  </si>
-  <si>
-    <t>96.2</t>
+185</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 1.775.849,92</t>
+  </si>
+  <si>
+    <t>R$ 9.106,92
+R$ 9.228,91</t>
+  </si>
+  <si>
+    <t>(5.6%)
+(4.3%)</t>
+  </si>
+  <si>
+    <t>95.8</t>
   </si>
   <si>
     <t>(9.8%)</t>
   </si>
   <si>
-    <t>45.6%</t>
-  </si>
-  <si>
-    <t>5.8%</t>
+    <t>44.7%</t>
+  </si>
+  <si>
+    <t>5.0%</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -947,10 +947,10 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>63.4%</t>
+    <t>28.6</t>
+  </si>
+  <si>
+    <t>63.7%</t>
   </si>
   <si>
     <t>12.4%</t>
@@ -968,13 +968,13 @@
     <t>20.2</t>
   </si>
   <si>
-    <t>67.4%</t>
-  </si>
-  <si>
-    <t>-R$ 51.789,03</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>67.2%</t>
+  </si>
+  <si>
+    <t>-R$ 51.894,03</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5994,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6030,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>7174.5299999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7174.5299999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.042324790794979084</v>
+      </c>
+      <c r="R36" s="7">
+        <v>81</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.17391304347826098</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.33710198438085842</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.014074552618777816</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.057573039627682933</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.023117820958306678</v>
+      </c>
+      <c r="X36" s="8">
+        <v>29.173383582089553</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.089552238805970144</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.8942382716049382</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>7.5156716417910445</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>13.825621</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>20.78358208955224</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.53731343283582089</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7915,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7951,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1239.5</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1239.5</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.38464364437913301</v>
+      </c>
+      <c r="R51" s="7">
+        <v>12</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.31878176684146831</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.031325131101250507</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.082559499798305763</v>
+      </c>
+      <c r="X51" s="8">
+        <v>25.388883333333336</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>6.0430583333333336</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>8.0416666666666661</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>14.369443</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>21.308333333333334</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12640,7 +12712,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12679,7 +12751,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12713,25 +12785,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>11478.18</v>
+      </c>
+      <c r="P89" s="5">
+        <v>11478.18</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.2088596950731989</v>
+      </c>
+      <c r="R89" s="7">
+        <v>109</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.20437956204379559</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.70459134636327359</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-1.053840094858244</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.017716876717388991</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.006561798124789818</v>
+      </c>
+      <c r="X89" s="8">
+        <v>39.456191428571429</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.37142857142857144</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>8.3888891891891895</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>9.1382352941176475</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>26.196665714285714</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-105</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15491,7 +15597,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15880,7 +15986,7 @@
         <v>-92.799999999999997</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16791,7 +16897,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17053,7 +17159,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17446,7 +17552,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18623,7 +18729,7 @@
         <v>-294.80000000000001</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18754,7 +18860,7 @@
         <v>-149.59999999999999</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20937,7 +21043,7 @@
         <v>-393.98000000000002</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21064,7 +21170,7 @@
         <v>-21.5</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22187,7 +22293,7 @@
         <v>-198.5</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28354,7 +28460,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
